--- a/downloads/Fantacalcio_2026_27_ListaGiocatori.xlsx
+++ b/downloads/Fantacalcio_2026_27_ListaGiocatori.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matortor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BC2C753-06CE-4A9B-9061-4CFBEF3843D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA21B8D-0081-4935-A1E8-38E63D2AA137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2126,13 +2126,13 @@
         <v>569</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>567</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>566</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>570</v>
